--- a/exports/colleges/10842_post-graduate-institute-of-medical-education-and-research-pgimer-chandigarh.xlsx
+++ b/exports/colleges/10842_post-graduate-institute-of-medical-education-and-research-pgimer-chandigarh.xlsx
@@ -605,19 +605,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="61" customWidth="1" min="2" max="2"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -707,12 +707,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>7,305</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with 45%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 June - 30 Jun 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>BPT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years 6 Months</t>
+          <t>4 years 6 months</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 50% marks in PCB</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>28 Oct - 31 Oct 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation with 50% marks</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Nov - 21 Nov 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10+2 with 55%</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 June - 16 Jul 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MBBS + INI-CET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>PGIMER, INI SS, INI CET</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 Jan - 07 Feb 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>MPH</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B.Sc (Nursing)</t>
+          <t>Master of Public Health [MPH]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B.Sc (Nursing)</t>
+          <t>Master of Public Health [MPH]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6,340 - 10,500</t>
+          <t>8,440</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>16 Apr - 06 May 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B.P.T</t>
+          <t>MDS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.P.T</t>
+          <t>Master of Dental Surgery [MDS]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.P.T</t>
+          <t>Master of Dental Surgery [MDS]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>9,210</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 Jan - 07 Feb 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Post Basic Bachelor of Science [P.B.B.Sc] (Nursing)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Post Basic Bachelor of Science [P.B.B.Sc] (Nursing)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15,600</t>
+          <t>6,340</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 June - 30 Jun 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>8,510</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>Ph.D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7,110 - 9,210</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1285,12 +1285,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>GATE / UGC NET</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>16 Apr - 06 May 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>MHA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>Master in Hospital Administration [MHA]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>Master in Hospital Administration [MHA]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8,440</t>
+          <t>5,240</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MDS</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDS</t>
+          <t>Master of Surgery [MS]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MDS</t>
+          <t>Master of Surgery [MS]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 Jan - 07 Feb 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Master in Audiology and Speech- Language Pathology [MASLP]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Master in Audiology and Speech- Language Pathology [MASLP]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8,510</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Nov - 21 Nov 2026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M.H.A [Hospital]</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M.H.A [Hospital]</t>
+          <t>Doctorate of Medicine [DM]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M.H.A [Hospital]</t>
+          <t>Doctorate of Medicine [DM]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5,240</t>
+          <t>8,510</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1560,27 +1560,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Optom</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Bachelor of Optometry [B.Optom]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nursing</t>
+          <t>Bachelor of Optometry [B.Optom]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15,600</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 June - 16 Jul 2026</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Medical Biotechnology</t>
+          <t>DM [Cardiac Anaesthesiology]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Medical Biotechnology</t>
+          <t>DM [Cardiac Anaesthesiology]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>8,510</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Anesthesia</t>
+          <t>Master of Chirurgiae [M.Ch]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Anesthesia</t>
+          <t>Master of Chirurgiae [M.Ch]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>8,510</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>23 Jan - 07 Feb 2026</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1746,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>BASLP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Bachelor in Audiology and Speech - Language Pathology [BASLP]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Bachelor in Audiology and Speech - Language Pathology [BASLP]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>10,500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 June - 16 Jul 2026</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor in Public Health [BPH]</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Bachelor in Public Health [BPH]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>10,500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>25 June - 16 Jul 2026</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor in Medical Laboratory Science [BMLS]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Anatomy</t>
+          <t>Bachelor in Medical Laboratory Science [BMLS]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Anatomy</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1932,27 +1932,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Master in Medical Laboratory Technology [MMLT]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Med.Tech. [Microbiology]</t>
+          <t>Master in Medical Laboratory Technology [MMLT]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Med.Tech. [Microbiology]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13,140</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1967,12 +1967,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Nov - 21 Nov 2026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1994,27 +1994,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Respiratory Technology</t>
+          <t>Post M.D. Certificate Course</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Respiratory Technology</t>
+          <t>Post M.D. Certificate Course</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6,440</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Med.Tech. [Pathology]</t>
+          <t>Doctor of Medicine [DM] (Medicine &amp; Microbiology)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Med.Tech. [Pathology]</t>
+          <t>Doctor of Medicine [DM] (Medicine &amp; Microbiology)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13,140</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2118,27 +2118,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Post Graduate Diploma in Public Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blood Transfusion Medicine</t>
+          <t>Post Graduate Diploma in Public Health</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Blood Transfusion Medicine</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13,140</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Speech And Hearing</t>
+          <t>Bachelor of Science [B.Sc] (Nursing)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Speech And Hearing</t>
+          <t>Bachelor of Science [B.Sc] (Nursing)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13,140</t>
+          <t>7,305</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 45%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -2242,17 +2242,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BPT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B.Sc (General)</t>
+          <t>Bachelor of Physiotherapy [BPT]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Bachelor of Physiotherapy [BPT]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2260,7 +2260,11 @@
           <t>10,500</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4 Years 6 Months</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2268,7 +2272,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% marks in PCB</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2300,25 +2304,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>M.D (General)</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>7,110 - 9,210</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>15,600</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2326,7 +2334,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation with 50% marks</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2346,7 +2354,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2358,25 +2366,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MPH</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MPH (General)</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>8,440</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4 Years</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2384,7 +2396,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 55%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2416,17 +2428,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MDS</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDS (General)</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2434,7 +2446,11 @@
           <t>9,210</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2442,12 +2458,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>MBBS + INI-CET</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>PGIMER, INI SS, INI CET</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2462,7 +2478,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -2474,25 +2490,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DM (General)</t>
+          <t>B.Sc (Nursing)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>B.Sc (Nursing)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8,510</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>6,340 - 10,500</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2532,51 +2552,1519 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>B.P.T</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B.P.T</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>B.P.T</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M.D</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M.D</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>M.D</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>7,110 - 9,210</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MPH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MPH</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>MPH</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>8,440</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>9,210</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>NEET PG</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>8,510</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NEET SS</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Doctorate</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>M.H.A [Hospital]</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M.H.A [Hospital]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>M.H.A [Hospital]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5,240</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Nursing</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>15,600</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Medical Biotechnology</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Medical Biotechnology</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Anesthesia</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Anesthesia</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pharmacology</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pharmacology</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Biochemistry</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Biochemistry</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Med.Tech. [Microbiology]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Med.Tech. [Microbiology]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>13,140</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Respiratory Technology</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Respiratory Technology</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>6,440</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Med.Tech. [Pathology]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Med.Tech. [Pathology]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>13,140</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Blood Transfusion Medicine</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Blood Transfusion Medicine</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>13,140</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M.Sc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Speech And Hearing</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Speech And Hearing</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>13,140</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2 Years</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IIT JAM</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B.Sc (General)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>10,500</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M.D</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>M.D (General)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>7,110 - 9,210</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MPH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MPH (General)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>8,440</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MDS</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MDS (General)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>9,210</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>DM</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DM (General)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8,510</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M.H.A [Hospital]</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>M.H.A [Hospital] (General)</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>5,240</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
